--- a/outputs/monitor_xlsx/20260612.xlsx
+++ b/outputs/monitor_xlsx/20260612.xlsx
@@ -44,10 +44,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00FF0000"/>
+      <color rgb="00008000"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="5">
@@ -101,8 +101,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1326,11 +1326,20 @@
       <c r="F4" t="n">
         <v>76563</v>
       </c>
+      <c r="G4" s="7" t="n">
+        <v>5759</v>
+      </c>
       <c r="H4" t="n">
-        <v>-16623</v>
+        <v>21841</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4830</v>
       </c>
       <c r="J4" t="n">
-        <v>10023</v>
+        <v>9335</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8453</v>
       </c>
       <c r="L4" t="n">
         <v>11438</v>
@@ -1375,11 +1384,20 @@
       <c r="F5" t="n">
         <v>2283</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>-219</v>
+      </c>
       <c r="H5" t="n">
-        <v>-1225</v>
+        <v>-422</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>-310</v>
+        <v>-64</v>
+      </c>
+      <c r="K5" t="n">
+        <v>37</v>
       </c>
       <c r="L5" t="n">
         <v>3613</v>
@@ -1424,11 +1442,20 @@
       <c r="F6" t="n">
         <v>9897</v>
       </c>
+      <c r="G6" s="7" t="n">
+        <v>715</v>
+      </c>
       <c r="H6" t="n">
-        <v>8591</v>
+        <v>9126</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-839</v>
       </c>
       <c r="J6" t="n">
-        <v>1143</v>
+        <v>1264</v>
+      </c>
+      <c r="K6" t="n">
+        <v>277</v>
       </c>
       <c r="L6" t="n">
         <v>5916</v>
@@ -1473,11 +1500,20 @@
       <c r="F7" t="n">
         <v>26306</v>
       </c>
+      <c r="G7" s="7" t="n">
+        <v>3927</v>
+      </c>
       <c r="H7" t="n">
-        <v>11314</v>
+        <v>13389</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-149</v>
       </c>
       <c r="J7" t="n">
-        <v>4347</v>
+        <v>3323</v>
+      </c>
+      <c r="K7" t="n">
+        <v>690</v>
       </c>
       <c r="L7" t="n">
         <v>27421</v>
@@ -1522,11 +1558,20 @@
       <c r="F8" t="n">
         <v>2814</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>-64</v>
+      </c>
       <c r="H8" t="n">
-        <v>617</v>
+        <v>1806</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-154</v>
       </c>
       <c r="J8" t="n">
-        <v>-290</v>
+        <v>-109</v>
+      </c>
+      <c r="K8" t="n">
+        <v>54</v>
       </c>
       <c r="L8" t="n">
         <v>1541</v>
@@ -1571,11 +1616,20 @@
       <c r="F9" t="n">
         <v>1795</v>
       </c>
+      <c r="G9" s="7" t="n">
+        <v>205</v>
+      </c>
       <c r="H9" t="n">
-        <v>44</v>
+        <v>231</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-155</v>
       </c>
       <c r="J9" t="n">
-        <v>-49</v>
+        <v>116</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
       </c>
       <c r="L9" t="n">
         <v>945</v>
@@ -1620,11 +1674,20 @@
       <c r="F10" t="n">
         <v>4224</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>-712</v>
+      </c>
       <c r="H10" t="n">
-        <v>314</v>
+        <v>-589</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-184</v>
       </c>
       <c r="J10" t="n">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="K10" t="n">
+        <v>377</v>
       </c>
       <c r="L10" t="n">
         <v>1980</v>
@@ -1669,11 +1732,20 @@
       <c r="F11" t="n">
         <v>860</v>
       </c>
+      <c r="G11" s="7" t="n">
+        <v>31</v>
+      </c>
       <c r="H11" t="n">
-        <v>-1062</v>
+        <v>-965</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-71</v>
       </c>
       <c r="J11" t="n">
-        <v>619</v>
+        <v>778</v>
+      </c>
+      <c r="K11" t="n">
+        <v>16</v>
       </c>
       <c r="L11" t="n">
         <v>6453</v>
@@ -1718,11 +1790,20 @@
       <c r="F12" t="n">
         <v>613</v>
       </c>
+      <c r="G12" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="H12" t="n">
-        <v>144</v>
+        <v>104</v>
+      </c>
+      <c r="I12" t="n">
+        <v>99</v>
       </c>
       <c r="J12" t="n">
-        <v>-399</v>
+        <v>-279</v>
+      </c>
+      <c r="K12" t="n">
+        <v>118</v>
       </c>
       <c r="L12" t="n">
         <v>348</v>
@@ -1767,12 +1848,21 @@
       <c r="F13" t="n">
         <v>3020</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>-31</v>
+      </c>
       <c r="H13" t="n">
         <v>-972</v>
       </c>
+      <c r="I13" t="n">
+        <v>-248</v>
+      </c>
       <c r="J13" t="n">
         <v>242</v>
       </c>
+      <c r="K13" t="n">
+        <v>34</v>
+      </c>
       <c r="L13" t="n">
         <v>127</v>
       </c>
@@ -1782,6 +1872,9 @@
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1813,12 +1906,21 @@
       <c r="F14" t="n">
         <v>1195</v>
       </c>
+      <c r="G14" s="7" t="n">
+        <v>283</v>
+      </c>
       <c r="H14" t="n">
         <v>-2025</v>
       </c>
+      <c r="I14" t="n">
+        <v>-94</v>
+      </c>
       <c r="J14" t="n">
         <v>-1134</v>
       </c>
+      <c r="K14" t="n">
+        <v>60</v>
+      </c>
       <c r="L14" t="n">
         <v>-105</v>
       </c>
@@ -1828,6 +1930,9 @@
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1859,12 +1964,21 @@
       <c r="F15" t="n">
         <v>1899</v>
       </c>
+      <c r="G15" s="6" t="n">
+        <v>-84</v>
+      </c>
       <c r="H15" t="n">
         <v>-973</v>
       </c>
+      <c r="I15" t="n">
+        <v>28</v>
+      </c>
       <c r="J15" t="n">
         <v>-23</v>
       </c>
+      <c r="K15" t="n">
+        <v>-1</v>
+      </c>
       <c r="L15" t="n">
         <v>-15</v>
       </c>
@@ -1874,6 +1988,9 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1905,11 +2022,20 @@
       <c r="F16" t="n">
         <v>94572</v>
       </c>
+      <c r="G16" s="7" t="n">
+        <v>25213</v>
+      </c>
       <c r="H16" t="n">
-        <v>93427</v>
+        <v>30761</v>
+      </c>
+      <c r="I16" t="n">
+        <v>944</v>
       </c>
       <c r="J16" t="n">
-        <v>-9187</v>
+        <v>-10147</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1288</v>
       </c>
       <c r="L16" t="n">
         <v>94273</v>
@@ -1954,11 +2080,20 @@
       <c r="F17" t="n">
         <v>15944</v>
       </c>
+      <c r="G17" s="7" t="n">
+        <v>2865</v>
+      </c>
       <c r="H17" t="n">
-        <v>9847</v>
+        <v>6176</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-8</v>
       </c>
       <c r="J17" t="n">
-        <v>3734</v>
+        <v>3265</v>
+      </c>
+      <c r="K17" t="n">
+        <v>329</v>
       </c>
       <c r="L17" t="n">
         <v>35544</v>
@@ -2003,11 +2138,20 @@
       <c r="F18" t="n">
         <v>1178</v>
       </c>
+      <c r="G18" s="7" t="n">
+        <v>36</v>
+      </c>
       <c r="H18" t="n">
-        <v>-2089</v>
+        <v>-1530</v>
+      </c>
+      <c r="I18" t="n">
+        <v>50</v>
       </c>
       <c r="J18" t="n">
-        <v>550</v>
+        <v>557</v>
+      </c>
+      <c r="K18" t="n">
+        <v>29</v>
       </c>
       <c r="L18" t="n">
         <v>1893</v>
@@ -2052,11 +2196,20 @@
       <c r="F19" t="n">
         <v>8765</v>
       </c>
+      <c r="G19" s="6" t="n">
+        <v>-232</v>
+      </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>1028</v>
+      </c>
+      <c r="I19" t="n">
+        <v>249</v>
       </c>
       <c r="J19" t="n">
-        <v>-4483</v>
+        <v>-3989</v>
+      </c>
+      <c r="K19" t="n">
+        <v>165</v>
       </c>
       <c r="L19" t="n">
         <v>10946</v>
@@ -2101,11 +2254,20 @@
       <c r="F20" t="n">
         <v>23826</v>
       </c>
+      <c r="G20" s="7" t="n">
+        <v>1664</v>
+      </c>
       <c r="H20" t="n">
-        <v>-16515</v>
+        <v>-14154</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-52</v>
       </c>
       <c r="J20" t="n">
-        <v>-2961</v>
+        <v>-3362</v>
+      </c>
+      <c r="K20" t="n">
+        <v>407</v>
       </c>
       <c r="L20" t="n">
         <v>8678</v>
@@ -2150,12 +2312,21 @@
       <c r="F21" t="n">
         <v>2765</v>
       </c>
+      <c r="G21" s="6" t="n">
+        <v>-40</v>
+      </c>
       <c r="H21" t="n">
         <v>-1600</v>
       </c>
+      <c r="I21" t="n">
+        <v>-33</v>
+      </c>
       <c r="J21" t="n">
         <v>-1818</v>
       </c>
+      <c r="K21" t="n">
+        <v>-2</v>
+      </c>
       <c r="L21" t="n">
         <v>44</v>
       </c>
@@ -2165,6 +2336,9 @@
       <c r="N21" t="n">
         <v>0</v>
       </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2196,11 +2370,20 @@
       <c r="F22" t="n">
         <v>50209</v>
       </c>
+      <c r="G22" s="6" t="n">
+        <v>-2703</v>
+      </c>
       <c r="H22" t="n">
-        <v>-4688</v>
+        <v>-5208</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5134</v>
       </c>
       <c r="J22" t="n">
-        <v>-3970</v>
+        <v>-1351</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1396</v>
       </c>
       <c r="L22" t="n">
         <v>26577</v>
@@ -2245,11 +2428,20 @@
       <c r="F23" t="n">
         <v>6276</v>
       </c>
+      <c r="G23" s="6" t="n">
+        <v>-1553</v>
+      </c>
       <c r="H23" t="n">
-        <v>170</v>
+        <v>-407</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-32</v>
       </c>
       <c r="J23" t="n">
-        <v>129</v>
+        <v>678</v>
+      </c>
+      <c r="K23" t="n">
+        <v>206</v>
       </c>
       <c r="L23" t="n">
         <v>4122</v>
@@ -2294,11 +2486,20 @@
       <c r="F24" t="n">
         <v>1785</v>
       </c>
+      <c r="G24" s="6" t="n">
+        <v>-635</v>
+      </c>
       <c r="H24" t="n">
-        <v>-1854</v>
+        <v>-2482</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>49</v>
+      </c>
+      <c r="K24" t="n">
+        <v>42</v>
       </c>
       <c r="L24" t="n">
         <v>10111</v>
@@ -2343,11 +2544,20 @@
       <c r="F25" t="n">
         <v>1850</v>
       </c>
+      <c r="G25" s="7" t="n">
+        <v>99</v>
+      </c>
       <c r="H25" t="n">
-        <v>-719</v>
+        <v>-207</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-81</v>
       </c>
       <c r="J25" t="n">
-        <v>-30</v>
+        <v>-216</v>
+      </c>
+      <c r="K25" t="n">
+        <v>60</v>
       </c>
       <c r="L25" t="n">
         <v>2434</v>
@@ -2392,12 +2602,21 @@
       <c r="F26" t="n">
         <v>20517</v>
       </c>
+      <c r="G26" s="7" t="n">
+        <v>1885</v>
+      </c>
       <c r="H26" t="n">
         <v>391</v>
       </c>
+      <c r="I26" t="n">
+        <v>652</v>
+      </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
+      <c r="K26" t="n">
+        <v>-837</v>
+      </c>
       <c r="L26" t="n">
         <v>332</v>
       </c>
@@ -2407,6 +2626,9 @@
       <c r="N26" t="n">
         <v>0</v>
       </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2438,15 +2660,24 @@
       <c r="F27" t="n">
         <v>509</v>
       </c>
+      <c r="G27" s="6" t="n">
+        <v>-5</v>
+      </c>
       <c r="H27" t="n">
         <v>293</v>
       </c>
       <c r="J27" t="n">
         <v>282</v>
       </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
       <c r="V27" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2478,11 +2709,20 @@
       <c r="F28" t="n">
         <v>4371</v>
       </c>
+      <c r="G28" s="6" t="n">
+        <v>-61</v>
+      </c>
       <c r="H28" t="n">
-        <v>6163</v>
+        <v>6902</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-696</v>
       </c>
       <c r="J28" t="n">
-        <v>3482</v>
+        <v>3178</v>
+      </c>
+      <c r="K28" t="n">
+        <v>107</v>
       </c>
       <c r="L28" t="n">
         <v>1625</v>
@@ -2527,12 +2767,18 @@
       <c r="F29" t="n">
         <v>17170</v>
       </c>
+      <c r="G29" s="6" t="n">
+        <v>-364</v>
+      </c>
       <c r="H29" t="n">
         <v>2024</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
+      <c r="K29" t="n">
+        <v>17</v>
+      </c>
       <c r="L29" t="n">
         <v>188</v>
       </c>
@@ -2540,6 +2786,9 @@
         <v>1976</v>
       </c>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">

--- a/outputs/monitor_xlsx/20260612.xlsx
+++ b/outputs/monitor_xlsx/20260612.xlsx
@@ -796,12 +796,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-103.55億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-2070.95億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-37.95億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-758.97億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-103.55億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-2070.95億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-37.95億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-758.97億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1330,13 +1330,13 @@
         <v>5759</v>
       </c>
       <c r="H4" t="n">
-        <v>21841</v>
+        <v>-16623</v>
       </c>
       <c r="I4" t="n">
         <v>4830</v>
       </c>
       <c r="J4" t="n">
-        <v>9335</v>
+        <v>10023</v>
       </c>
       <c r="K4" t="n">
         <v>8453</v>
@@ -1388,13 +1388,13 @@
         <v>-219</v>
       </c>
       <c r="H5" t="n">
-        <v>-422</v>
+        <v>-1225</v>
       </c>
       <c r="I5" t="n">
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>-64</v>
+        <v>-310</v>
       </c>
       <c r="K5" t="n">
         <v>37</v>
@@ -1446,13 +1446,13 @@
         <v>715</v>
       </c>
       <c r="H6" t="n">
-        <v>9126</v>
+        <v>8591</v>
       </c>
       <c r="I6" t="n">
         <v>-839</v>
       </c>
       <c r="J6" t="n">
-        <v>1264</v>
+        <v>1143</v>
       </c>
       <c r="K6" t="n">
         <v>277</v>
@@ -1504,13 +1504,13 @@
         <v>3927</v>
       </c>
       <c r="H7" t="n">
-        <v>13389</v>
+        <v>11314</v>
       </c>
       <c r="I7" t="n">
         <v>-149</v>
       </c>
       <c r="J7" t="n">
-        <v>3323</v>
+        <v>4347</v>
       </c>
       <c r="K7" t="n">
         <v>690</v>
@@ -1562,13 +1562,13 @@
         <v>-64</v>
       </c>
       <c r="H8" t="n">
-        <v>1806</v>
+        <v>617</v>
       </c>
       <c r="I8" t="n">
         <v>-154</v>
       </c>
       <c r="J8" t="n">
-        <v>-109</v>
+        <v>-290</v>
       </c>
       <c r="K8" t="n">
         <v>54</v>
@@ -1620,13 +1620,13 @@
         <v>205</v>
       </c>
       <c r="H9" t="n">
-        <v>231</v>
+        <v>44</v>
       </c>
       <c r="I9" t="n">
         <v>-155</v>
       </c>
       <c r="J9" t="n">
-        <v>116</v>
+        <v>-49</v>
       </c>
       <c r="K9" t="n">
         <v>20</v>
@@ -1678,13 +1678,13 @@
         <v>-712</v>
       </c>
       <c r="H10" t="n">
-        <v>-589</v>
+        <v>314</v>
       </c>
       <c r="I10" t="n">
         <v>-184</v>
       </c>
       <c r="J10" t="n">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="K10" t="n">
         <v>377</v>
@@ -1736,13 +1736,13 @@
         <v>31</v>
       </c>
       <c r="H11" t="n">
-        <v>-965</v>
+        <v>-1062</v>
       </c>
       <c r="I11" t="n">
         <v>-71</v>
       </c>
       <c r="J11" t="n">
-        <v>778</v>
+        <v>619</v>
       </c>
       <c r="K11" t="n">
         <v>16</v>
@@ -1794,13 +1794,13 @@
         <v>40</v>
       </c>
       <c r="H12" t="n">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="I12" t="n">
         <v>99</v>
       </c>
       <c r="J12" t="n">
-        <v>-279</v>
+        <v>-399</v>
       </c>
       <c r="K12" t="n">
         <v>118</v>
@@ -1834,20 +1834,7 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2195</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3020</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="G13" s="6" t="n">
         <v>-31</v>
       </c>
@@ -1872,9 +1859,6 @@
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1892,20 +1876,7 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>501</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1195</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="G14" s="7" t="n">
         <v>283</v>
       </c>
@@ -1930,9 +1901,6 @@
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1950,20 +1918,7 @@
           <t>上詮</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>737</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1899</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="G15" s="6" t="n">
         <v>-84</v>
       </c>
@@ -1988,9 +1943,6 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2026,13 +1978,13 @@
         <v>25213</v>
       </c>
       <c r="H16" t="n">
-        <v>30761</v>
+        <v>93427</v>
       </c>
       <c r="I16" t="n">
         <v>944</v>
       </c>
       <c r="J16" t="n">
-        <v>-10147</v>
+        <v>-9187</v>
       </c>
       <c r="K16" t="n">
         <v>1288</v>
@@ -2084,13 +2036,13 @@
         <v>2865</v>
       </c>
       <c r="H17" t="n">
-        <v>6176</v>
+        <v>9847</v>
       </c>
       <c r="I17" t="n">
         <v>-8</v>
       </c>
       <c r="J17" t="n">
-        <v>3265</v>
+        <v>3734</v>
       </c>
       <c r="K17" t="n">
         <v>329</v>
@@ -2142,13 +2094,13 @@
         <v>36</v>
       </c>
       <c r="H18" t="n">
-        <v>-1530</v>
+        <v>-2089</v>
       </c>
       <c r="I18" t="n">
         <v>50</v>
       </c>
       <c r="J18" t="n">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="K18" t="n">
         <v>29</v>
@@ -2200,13 +2152,13 @@
         <v>-232</v>
       </c>
       <c r="H19" t="n">
-        <v>1028</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
         <v>249</v>
       </c>
       <c r="J19" t="n">
-        <v>-3989</v>
+        <v>-4483</v>
       </c>
       <c r="K19" t="n">
         <v>165</v>
@@ -2258,13 +2210,13 @@
         <v>1664</v>
       </c>
       <c r="H20" t="n">
-        <v>-14154</v>
+        <v>-16515</v>
       </c>
       <c r="I20" t="n">
         <v>-52</v>
       </c>
       <c r="J20" t="n">
-        <v>-3362</v>
+        <v>-2961</v>
       </c>
       <c r="K20" t="n">
         <v>407</v>
@@ -2298,20 +2250,7 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>860</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2765</v>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="G21" s="6" t="n">
         <v>-40</v>
       </c>
@@ -2336,9 +2275,6 @@
       <c r="N21" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="V21" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2374,13 +2310,13 @@
         <v>-2703</v>
       </c>
       <c r="H22" t="n">
-        <v>-5208</v>
+        <v>-4688</v>
       </c>
       <c r="I22" t="n">
         <v>5134</v>
       </c>
       <c r="J22" t="n">
-        <v>-1351</v>
+        <v>-3970</v>
       </c>
       <c r="K22" t="n">
         <v>1396</v>
@@ -2432,13 +2368,13 @@
         <v>-1553</v>
       </c>
       <c r="H23" t="n">
-        <v>-407</v>
+        <v>170</v>
       </c>
       <c r="I23" t="n">
         <v>-32</v>
       </c>
       <c r="J23" t="n">
-        <v>678</v>
+        <v>129</v>
       </c>
       <c r="K23" t="n">
         <v>206</v>
@@ -2490,13 +2426,13 @@
         <v>-635</v>
       </c>
       <c r="H24" t="n">
-        <v>-2482</v>
+        <v>-1854</v>
       </c>
       <c r="I24" t="n">
         <v>-2</v>
       </c>
       <c r="J24" t="n">
-        <v>49</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="n">
         <v>42</v>
@@ -2548,13 +2484,13 @@
         <v>99</v>
       </c>
       <c r="H25" t="n">
-        <v>-207</v>
+        <v>-572</v>
       </c>
       <c r="I25" t="n">
         <v>-81</v>
       </c>
       <c r="J25" t="n">
-        <v>-216</v>
+        <v>-97</v>
       </c>
       <c r="K25" t="n">
         <v>60</v>
@@ -2588,20 +2524,7 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>276.5</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="F26" t="n">
-        <v>20517</v>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="G26" s="7" t="n">
         <v>1885</v>
       </c>
@@ -2626,9 +2549,6 @@
       <c r="N26" t="n">
         <v>0</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2646,20 +2566,7 @@
           <t>創新服務</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1920</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="F27" t="n">
-        <v>509</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="G27" s="6" t="n">
         <v>-5</v>
       </c>
@@ -2675,9 +2582,6 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
       <c r="V27" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2713,13 +2617,13 @@
         <v>-61</v>
       </c>
       <c r="H28" t="n">
-        <v>6902</v>
+        <v>6163</v>
       </c>
       <c r="I28" t="n">
         <v>-696</v>
       </c>
       <c r="J28" t="n">
-        <v>3178</v>
+        <v>3482</v>
       </c>
       <c r="K28" t="n">
         <v>107</v>
@@ -2753,20 +2657,7 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>124</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="F29" t="n">
-        <v>17170</v>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="G29" s="6" t="n">
         <v>-364</v>
       </c>
@@ -2786,9 +2677,6 @@
         <v>1976</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
